--- a/mistral_translate_work/split_by_prompt/excel/quest/lang_multi_text/lang_multi_text__quest__part_0034.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/quest/lang_multi_text/lang_multi_text__quest__part_0034.xlsx
@@ -10519,7 +10519,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Đi</t>
+          <t>Đi thôi</t>
         </is>
       </c>
     </row>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=Ấn} "Nâng cấp Cube" ở góc dưới bên phải để tăng sức mạnh cho Cube của cậu</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} "Nâng cấp Cube" ở góc dưới bên phải để tăng sức mạnh cho Cube của cậu</t>
         </is>
       </c>
     </row>
@@ -19361,7 +19361,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=Ấn} "Nâng cấp Cube" và nâng cấp 3 Cube lên cấp 4</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} "Nâng cấp Cube" và nâng cấp 3 Cube lên cấp 4</t>
         </is>
       </c>
     </row>
@@ -19426,7 +19426,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=Ấn} "Nâng cấp Cube" và nâng cấp 5 Cube lên cấp 10</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} "Nâng cấp Cube" và nâng cấp 5 Cube lên cấp 10</t>
         </is>
       </c>
     </row>
